--- a/frontend/public/templates/actor-import-template.xlsx
+++ b/frontend/public/templates/actor-import-template.xlsx
@@ -13,12 +13,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="114">
   <si>
     <t>ACCELERATE Tanzania — Actor Import Template</t>
   </si>
   <si>
-    <t>Template version: v1</t>
+    <t>Template version: v2</t>
   </si>
   <si>
     <t>How to use this template</t>
@@ -75,7 +75,7 @@
     <t>Choose from the dropdown</t>
   </si>
   <si>
-    <t>seed_company, cooperative, ngo, offtaker, research_institute, informal_trader</t>
+    <t>seed_company, cooperative, ngo, offtaker, research_institute, informal_trader, humanitarian, digital_service_provider, qds_producer, bulk_buyer</t>
   </si>
   <si>
     <t>Region</t>
@@ -165,6 +165,30 @@
     <t>GRANTED, DENIED, UNKNOWN</t>
   </si>
   <si>
+    <t>Registration Source</t>
+  </si>
+  <si>
+    <t>TEAM_MANAGED, SELF_REGISTERED</t>
+  </si>
+  <si>
+    <t>Consent Method</t>
+  </si>
+  <si>
+    <t>NOT_RECORDED, PORTAL_CHECKBOX, SIGNED_FORM, EMAIL, VERBAL_FIELD</t>
+  </si>
+  <si>
+    <t>Consent Obtained At</t>
+  </si>
+  <si>
+    <t>Date consent was obtained, e.g. 2026-01-15</t>
+  </si>
+  <si>
+    <t>Consent Reference</t>
+  </si>
+  <si>
+    <t>Free text pointer to the evidence, e.g. document ID or email thread (max 255 chars)</t>
+  </si>
+  <si>
     <t>seed_company</t>
   </si>
   <si>
@@ -180,6 +204,12 @@
     <t>GRANTED</t>
   </si>
   <si>
+    <t>TEAM_MANAGED</t>
+  </si>
+  <si>
+    <t>NOT_RECORDED</t>
+  </si>
+  <si>
     <t>cooperative</t>
   </si>
   <si>
@@ -195,6 +225,12 @@
     <t>DENIED</t>
   </si>
   <si>
+    <t>SELF_REGISTERED</t>
+  </si>
+  <si>
+    <t>PORTAL_CHECKBOX</t>
+  </si>
+  <si>
     <t>ngo</t>
   </si>
   <si>
@@ -207,31 +243,52 @@
     <t>UNKNOWN</t>
   </si>
   <si>
+    <t>SIGNED_FORM</t>
+  </si>
+  <si>
     <t>offtaker</t>
   </si>
   <si>
     <t>Geita</t>
   </si>
   <si>
+    <t>EMAIL</t>
+  </si>
+  <si>
     <t>research_institute</t>
   </si>
   <si>
     <t>Iringa</t>
   </si>
   <si>
+    <t>VERBAL_FIELD</t>
+  </si>
+  <si>
     <t>informal_trader</t>
   </si>
   <si>
     <t>Kagera</t>
   </si>
   <si>
+    <t>humanitarian</t>
+  </si>
+  <si>
     <t>Katavi</t>
   </si>
   <si>
+    <t>digital_service_provider</t>
+  </si>
+  <si>
     <t>Kigoma</t>
   </si>
   <si>
+    <t>qds_producer</t>
+  </si>
+  <si>
     <t>Kilimanjaro</t>
+  </si>
+  <si>
+    <t>bulk_buyer</t>
   </si>
   <si>
     <t>Lindi</t>
@@ -683,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1031,6 +1088,62 @@
         <v>49</v>
       </c>
     </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>50</v>
+      </c>
+      <c r="B33" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" t="s">
+        <v>57</v>
+      </c>
+      <c r="D36" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1039,7 +1152,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="5" width="14" customWidth="1"/>
@@ -1053,9 +1166,13 @@
     <col min="18" max="18" width="19" customWidth="1"/>
     <col min="19" max="19" width="17" customWidth="1"/>
     <col min="20" max="20" width="16" customWidth="1"/>
+    <col min="21" max="21" width="21" customWidth="1"/>
+    <col min="22" max="22" width="16" customWidth="1"/>
+    <col min="23" max="23" width="21" customWidth="1"/>
+    <col min="24" max="24" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>13</v>
       </c>
@@ -1116,11 +1233,23 @@
       <c r="T1" s="2" t="s">
         <v>48</v>
       </c>
+      <c r="U1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>56</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="7">
+  <dataValidations count="9">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="error" errorTitle="Invalid value" error="Choose a value from the dropdown list." sqref="C2:C1001">
-      <formula1>Lists!$A$1:$A$6</formula1>
+      <formula1>Lists!$A$1:$A$10</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="error" errorTitle="Invalid value" error="Choose a value from the dropdown list." sqref="D2:D1001">
       <formula1>Lists!$B$1:$B$31</formula1>
@@ -1140,6 +1269,12 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="error" errorTitle="Invalid value" error="Choose a value from the dropdown list." sqref="T2:T1001">
       <formula1>Lists!$G$1:$G$3</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="error" errorTitle="Invalid value" error="Choose a value from the dropdown list." sqref="U2:U1001">
+      <formula1>Lists!$H$1:$H$2</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="error" errorTitle="Invalid value" error="Choose a value from the dropdown list." sqref="V2:V1001">
+      <formula1>Lists!$I$1:$I$5</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1148,216 +1283,249 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="F1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="G1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="H1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+      <c r="H2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="G3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="I3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="I4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>81</v>
+      </c>
+      <c r="I5" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>85</v>
+      </c>
       <c r="B7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>87</v>
+      </c>
       <c r="B8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>89</v>
+      </c>
       <c r="B9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>91</v>
+      </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/public/templates/actor-import-template.xlsx
+++ b/frontend/public/templates/actor-import-template.xlsx
@@ -13,12 +13,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="118">
   <si>
     <t>ACCELERATE Tanzania — Actor Import Template</t>
   </si>
   <si>
-    <t>Template version: v2</t>
+    <t>Template version: v3</t>
   </si>
   <si>
     <t>How to use this template</t>
@@ -187,6 +187,18 @@
   </si>
   <si>
     <t>Free text pointer to the evidence, e.g. document ID or email thread (max 255 chars)</t>
+  </si>
+  <si>
+    <t>Contact Person</t>
+  </si>
+  <si>
+    <t>Free text, e.g. Jane Mwangi (max 120 chars)</t>
+  </si>
+  <si>
+    <t>Other Crops</t>
+  </si>
+  <si>
+    <t>Free text, e.g. Sesame, Sunflower (max 300 chars)</t>
   </si>
   <si>
     <t>seed_company</t>
@@ -740,7 +752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1144,6 +1156,34 @@
         <v>16</v>
       </c>
     </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" t="s">
+        <v>59</v>
+      </c>
+      <c r="D37" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>60</v>
+      </c>
+      <c r="B38" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" t="s">
+        <v>61</v>
+      </c>
+      <c r="D38" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1152,7 +1192,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:Z1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="5" width="14" customWidth="1"/>
@@ -1170,9 +1210,11 @@
     <col min="22" max="22" width="16" customWidth="1"/>
     <col min="23" max="23" width="21" customWidth="1"/>
     <col min="24" max="24" width="19" customWidth="1"/>
+    <col min="25" max="25" width="16" customWidth="1"/>
+    <col min="26" max="26" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>13</v>
       </c>
@@ -1244,6 +1286,12 @@
       </c>
       <c r="X1" s="2" t="s">
         <v>56</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1288,244 +1336,244 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="I1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
